--- a/out/Attention-Mamba1_repeat_4_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.2742121623455774</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.091217805496784</v>
+        <v>3.713372298387599</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.091217805496784</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC44" t="n">
         <v>-0.0004499999204052146</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.091217805496784</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC45" t="n">
         <v>1.159465998829599</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.216984246204107</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC46" t="n">
         <v>0.4449770803534591</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.216984246204107</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC47" t="n">
         <v>0.4449770803534591</v>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4449320688384282</v>
+        <v>0.4444534596596933</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1382851087847584</v>
+        <v>1.608675852071151</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.816984246204107</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7217776443806274</v>
+        <v>3.665008738600448</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02645929741725322</v>
+        <v>0.3078019982914837</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>3.491217805496785</v>
+        <v>3.113372298387599</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.636209330376971</v>
+        <v>2.669589134883752</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04634575123887046</v>
+        <v>0.5391446088976497</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7024549410610458</v>
+        <v>3.440227112427471</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02538061992790095</v>
+        <v>0.2952552076258361</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7068305239536155</v>
+        <v>3.491128208704679</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01048156037921247</v>
+        <v>0.121944700635907</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7023873402332431</v>
+        <v>3.439452882856035</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0130602144509285</v>
+        <v>0.1519321419831171</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7180272225974256</v>
+        <v>3.621393915714624</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.007861903601196077</v>
+        <v>0.0914827749081388</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7206837248736627</v>
+        <v>3.652324423167279</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.005975906584048601</v>
+        <v>0.0695515020846839</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7247709460212218</v>
+        <v>3.699906176494566</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002639581997095357</v>
+        <v>0.03076360476574889</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7240715750448341</v>
+        <v>3.69181874318781</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002093480228627121</v>
+        <v>0.024409891334685</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7256191258419091</v>
+        <v>3.709866365108923</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0010356157895349</v>
+        <v>0.01210466595465973</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.491217805496785</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7255955326762991</v>
+        <v>3.709645237626453</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0006001137550909445</v>
+        <v>0.007035265804423489</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7257600029784064</v>
+        <v>3.711607618250681</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.003515132902211744</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7257546262746696</v>
+        <v>3.71159823544759</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001444817044438485</v>
+        <v>0.00173416213824093</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7257458077013755</v>
+        <v>3.711549175710904</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.177897222547117e-05</v>
+        <v>0.001006308791704529</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.491217805496785</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7257652688687726</v>
+        <v>3.711823840125214</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>0.0003320274872097581</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7257303430592112</v>
+        <v>3.711482991685591</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.07205380308973e-05</v>
+        <v>0.0001656801271925993</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7257255170104264</v>
+        <v>3.711479880298784</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>8.795545294412324e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7257219123330957</v>
+        <v>3.711490012873</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>4.003342849230196e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7257166019559498</v>
+        <v>3.711482064290114</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>2.118280671066587e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.491217805496785</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7257126776695987</v>
+        <v>3.711487285380855</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>7.887479732251461e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7257123455662755</v>
+        <v>3.711478948229486</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7257127261013333</v>
+        <v>3.711475843544236</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7257129544223679</v>
+        <v>3.711471524553087</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-1.724541871943372e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7257130443670179</v>
+        <v>3.711466700380198</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.725712186433433</v>
+        <v>3.711465842446613</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7257124147544678</v>
+        <v>3.711466070767647</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7257116190902561</v>
+        <v>3.711465275103436</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7257116813596292</v>
+        <v>3.711465337372809</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.725711709034906</v>
+        <v>3.711465365048086</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7257118612489293</v>
+        <v>3.711465517262109</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7257115153079675</v>
+        <v>3.711465171321147</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7257115914149792</v>
+        <v>3.711465247428158</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7257117574666407</v>
+        <v>3.71146541347982</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7257121172452409</v>
+        <v>3.71146577325842</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7257121380016985</v>
+        <v>3.711465794014878</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7257122417839871</v>
+        <v>3.711465897797166</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7257124701050217</v>
+        <v>3.711466126118201</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7257123455662755</v>
+        <v>3.711466001579455</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7257123732415524</v>
+        <v>3.711466029254732</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7257124285921063</v>
+        <v>3.711466084605286</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7257126915072371</v>
+        <v>3.711466347520417</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7257126084814063</v>
+        <v>3.711466264494586</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7257124009168294</v>
+        <v>3.711466056930009</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7257124147544678</v>
+        <v>3.711466070767647</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7257125531308525</v>
+        <v>3.711466209144032</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7257122694592639</v>
+        <v>3.711465925472444</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7257120964887831</v>
+        <v>3.711465752501963</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7257119927064947</v>
+        <v>3.711465648719674</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7257121380016985</v>
+        <v>3.711465794014878</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7257123801603718</v>
+        <v>3.711466036173551</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7257122071898908</v>
+        <v>3.71146586320307</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7257119096806638</v>
+        <v>3.711465565693843</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7257118958430253</v>
+        <v>3.711465551856205</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7257115291456061</v>
+        <v>3.711465185158786</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7257115291456061</v>
+        <v>3.711465185158786</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.725711466876233</v>
+        <v>3.711465122889412</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7257113630939445</v>
+        <v>3.711465019107124</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7257111901234637</v>
+        <v>3.711464846136644</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7257112385551983</v>
+        <v>3.711464894568378</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7257108787765982</v>
+        <v>3.711464534789777</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7257108372636829</v>
+        <v>3.711464493276862</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7257108926142366</v>
+        <v>3.711464548627417</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7257109479647905</v>
+        <v>3.71146460397797</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.725710989477706</v>
+        <v>3.711464645490886</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7257107196437558</v>
+        <v>3.711464375656935</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7257107749943098</v>
+        <v>3.71146443100749</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7257109202895137</v>
+        <v>3.711464576302693</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7257108856954174</v>
+        <v>3.711464541708597</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7257108718577788</v>
+        <v>3.711464527870959</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.725710961802429</v>
+        <v>3.711464617815608</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>4.091217805496784</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7257112800681137</v>
+        <v>3.711464936081293</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7257111001788136</v>
+        <v>3.711464756191993</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.725711141691729</v>
+        <v>3.711464797704909</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7257109548836097</v>
+        <v>3.711464610896789</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7257110240718021</v>
+        <v>3.711464680084982</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7257108234260443</v>
+        <v>3.711464479439224</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7257108649389598</v>
+        <v>3.711464520952139</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.8742121623455774</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7257108926142366</v>
+        <v>3.711464548627417</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>4.091217805496784</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.216984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>4.091217805496784</v>
+        <v>1.774960311951877</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>4.091217805496784</v>
+        <v>2.75969220948351</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004499999204052146</v>
+        <v>-0.0004167827583421021</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5791847404061293</v>
+        <v>0.5364318758007453</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>4.091217805496784</v>
+        <v>1.774960311951877</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.159465998829599</v>
+        <v>1.073878938749222</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.133757660132265</v>
+        <v>-0.1238841692053108</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.216984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.4121309238370923</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4449770803534591</v>
+        <v>0.4121309238370923</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4449320688384282</v>
+        <v>0.4120366583910854</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1382851087847584</v>
+        <v>0.2896036745883149</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7217776443806274</v>
+        <v>0.9918210013567917</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02645929741725322</v>
+        <v>0.05541239997857398</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>3.491217805496785</v>
+        <v>1.574960311951877</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.636209330376971</v>
+        <v>0.8126193061932309</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04634575123887046</v>
+        <v>0.09706007376861901</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>4.091217805496784</v>
+        <v>2.75969220948351</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7024549410610458</v>
+        <v>0.9513545278310983</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02538061992790095</v>
+        <v>0.05315386673158558</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>4.091217805496784</v>
+        <v>1.774960311951877</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7068305239536155</v>
+        <v>0.9605180921582652</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01048156037921247</v>
+        <v>0.02195312424383977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.216984246204107</v>
+        <v>1.774960311951877</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7023873402332431</v>
+        <v>0.9512151460905764</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0130602144509285</v>
+        <v>0.02735170891763205</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>4.091217805496784</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7180272225974256</v>
+        <v>0.9839697125152478</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.007861903601196077</v>
+        <v>0.01646926185337869</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.816984246204107</v>
+        <v>1.774960311951877</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7206837248736627</v>
+        <v>0.9895381671030145</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.005975906584048601</v>
+        <v>0.01252094794352263</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>4.091217805496784</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7247709460212218</v>
+        <v>0.9981035984159559</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002639581997095357</v>
+        <v>0.005535272140549529</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7240715750448341</v>
+        <v>0.9966443594414534</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002093480228627121</v>
+        <v>0.004391215190501288</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7256191258419091</v>
+        <v>0.999889921949317</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0010356157895349</v>
+        <v>0.002173789309338696</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.491217805496785</v>
+        <v>1.574960311951877</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7255955326762991</v>
+        <v>0.9998460152111962</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0006001137550909445</v>
+        <v>0.00126341152509448</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>4.091217805496784</v>
+        <v>1.574960311951877</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7257600029784064</v>
+        <v>1.000195395365104</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.00062920576254724</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.216984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7257546262746696</v>
+        <v>1.000189605736117</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001444817044438485</v>
+        <v>0.0003083366496996056</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7257458077013755</v>
+        <v>1.000176673933569</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.177897222547117e-05</v>
+        <v>0.0001752332500067478</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.491217805496785</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7257652688687726</v>
+        <v>1.000221978677206</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.40156114816348e-05</v>
+        <v>5.526319307724151e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7257303430592112</v>
+        <v>1.000156017238508</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.07205380308973e-05</v>
+        <v>2.644107606179461e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7257255170104264</v>
+        <v>1.000151365140938</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>1.212337291075954e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7257219123330957</v>
+        <v>1.000149152720399</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7257166019559498</v>
+        <v>1.000143611047668</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>3.491217805496785</v>
+        <v>0.5902284144202447</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7257126776695987</v>
+        <v>1.000140762474966</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.216984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7257123455662755</v>
+        <v>1.000135095044693</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7257127261013333</v>
+        <v>1.00013547557975</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7257129544223679</v>
+        <v>1.000135703900785</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7257130443670179</v>
+        <v>1.000135793845435</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.725712186433433</v>
+        <v>1.00013493591185</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7257124147544678</v>
+        <v>1.000135164232885</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7257116190902561</v>
+        <v>1.000134368568673</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7257116813596292</v>
+        <v>1.000134430838046</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.725711709034906</v>
+        <v>1.000134458513323</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7257118612489293</v>
+        <v>1.000134610727346</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7257115153079675</v>
+        <v>1.000134264786384</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7257115914149792</v>
+        <v>1.000134340893396</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7257117574666407</v>
+        <v>1.000134506945058</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7257121172452409</v>
+        <v>1.000134866723658</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7257121380016985</v>
+        <v>1.000134887480115</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>4.091217805496784</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7257122417839871</v>
+        <v>1.000134991262404</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.216984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7257124701050217</v>
+        <v>1.000135219583439</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7257123455662755</v>
+        <v>1.000135095044693</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7257123732415524</v>
+        <v>1.000135122719969</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7257124285921063</v>
+        <v>1.000135178070523</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7257126915072371</v>
+        <v>1.000135440985654</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7257126084814063</v>
+        <v>1.000135357959823</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7257124009168294</v>
+        <v>1.000135150395246</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7257124147544678</v>
+        <v>1.000135164232885</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7257125531308525</v>
+        <v>1.000135302609269</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7257122694592639</v>
+        <v>1.000135018937681</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7257120964887831</v>
+        <v>1.0001348459672</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7257119927064947</v>
+        <v>1.000134742184912</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7257121380016985</v>
+        <v>1.000134887480115</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7257123801603718</v>
+        <v>1.000135129638789</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7257122071898908</v>
+        <v>1.000134956668308</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7257119096806638</v>
+        <v>1.000134659159081</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7257118958430253</v>
+        <v>1.000134645321442</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7257115291456061</v>
+        <v>1.000134278624023</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7257115291456061</v>
+        <v>1.000134278624023</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.725711466876233</v>
+        <v>1.00013421635465</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7257113630939445</v>
+        <v>1.000134112572362</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7257111901234637</v>
+        <v>1.000133939601881</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7257112385551983</v>
+        <v>1.000133988033615</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7257108787765982</v>
+        <v>1.000133628255015</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7257108372636829</v>
+        <v>1.0001335867421</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7257108926142366</v>
+        <v>1.000133642092654</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7257109479647905</v>
+        <v>1.000133697443208</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.725710989477706</v>
+        <v>1.000133738956123</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7257107196437558</v>
+        <v>1.000133469122173</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7257107749943098</v>
+        <v>1.000133524472727</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7257109202895137</v>
+        <v>1.000133669767931</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7257108856954174</v>
+        <v>1.000133635173834</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7257108718577788</v>
+        <v>1.000133621336196</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.816984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.725710961802429</v>
+        <v>1.000133711280846</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>4.091217805496784</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7257112800681137</v>
+        <v>1.000134029546531</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.216984246204107</v>
+        <v>0.7902284144202447</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7257111001788136</v>
+        <v>1.000133849657231</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.216984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.725711141691729</v>
+        <v>1.000133891170146</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.1945034831113877</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7257109548836097</v>
+        <v>1.000133704362027</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7257110240718021</v>
+        <v>1.000133773550219</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7257108234260443</v>
+        <v>1.000133572904461</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7257108649389598</v>
+        <v>1.000133614417377</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.816984246204107</v>
+        <v>-0.3945034831113877</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7257108926142366</v>
+        <v>1.000133642092654</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.001149719581007957</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001093912869691849</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.04999999999999971</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001104498282074928</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001155907288193703</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001549901440739632</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.16</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001257250085473061</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001570826396346092</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001206373795866966</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001257086172699928</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001694208011031151</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001719655469059944</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001840399578213692</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.001553555950522423</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001945154741406441</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002032382413744926</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.002063222229480743</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001819757744669914</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001610806211829185</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001261170953512192</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001651650294661522</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00179041363298893</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.00193432904779911</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001939682289958</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.00142686627805233</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001941932365298271</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.000985490158200264</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.000218292698264122</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0008589606732130051</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.001233404502272606</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1945034831113877</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001110436394810677</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1945034831113877</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.00164218433201313</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001874817535281181</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001637896522879601</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0006378982216119766</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001331793144345284</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.001297602429986</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.001015147194266319</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.001502742990851402</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.001310920342803001</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0009707864373922348</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0003504734486341476</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0001511033624410629</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.774960311951877</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.001502273604273796</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.75969220948351</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004167827583421021</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5364318758007453</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.001021979376673698</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.774960311951877</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.073878938749222</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1238841692053108</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0006977580487728119</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4121309238370923</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-6.519816815853119e-05</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1945034831113877</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4121309238370923</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0001495927572250366</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4120366583910854</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.2896036745883149</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0007520373910665512</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.9918210013567917</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.05541239997857398</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0004364103078842163</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.574960311951877</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8126193061932309</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.09706007376861901</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>7.568858563899994e-05</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.75969220948351</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9513545278310983</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.05315386673158558</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0001615341752767563</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.774960311951877</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9605180921582652</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.02195312424383977</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0006300788372755051</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.774960311951877</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9512151460905764</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.02735170891763205</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001656441017985344</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7902284144202447</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.9839697125152478</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01646926185337869</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0008706841617822647</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.774960311951877</v>
+        <v>-0.3</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.9895381671030145</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01252094794352263</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.00293884240090847</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.9981035984159559</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.005535272140549529</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002332659438252449</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.9966443594414534</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.004391215190501288</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.00552862323820591</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.999889921949317</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.002173789309338696</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.005274025723338127</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.574960311951877</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.9998460152111962</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00126341152509448</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.005262864753603935</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.574960311951877</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.000195395365104</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00062920576254724</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0009346604347229004</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7902284144202447</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.000189605736117</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0003083366496996056</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.002454893663525581</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.000176673933569</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0001752332500067478</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.0004567783325910568</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.000221978677206</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>5.526319307724151e-05</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001624139025807381</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.000156017238508</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>2.644107606179461e-05</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.00135795958340168</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.000151365140938</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.212337291075954e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001973794773221016</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.000149152720399</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.110541340889784e-06</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.001015087589621544</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.000143611047668</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0002600569278001785</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5902284144202447</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.000140762474966</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0009745452553033829</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7902284144202447</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.000135095044693</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0005184095352888107</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.00013547557975</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.002309849485754967</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.000135703900785</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.001269010826945305</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.000135793845435</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001947948709130287</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.00013493591185</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0003470946103334427</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.000135164232885</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0002161022275686264</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.000134368568673</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001512933522462845</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.000134430838046</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001611316576600075</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.000134458513323</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0003103259950876236</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.000134610727346</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001415975391864777</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.000134264786384</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.001457519829273224</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.000134340893396</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002230484038591385</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.000134506945058</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.00086217001080513</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.000134866723658</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.0001916978508234024</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.000134887480115</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.0002622436732053757</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.000134991262404</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001870037987828255</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.000135219583439</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002738794311881065</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1945034831113877</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.000135095044693</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003211705014109612</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.000135122719969</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.001273661851882935</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.000135178070523</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001403609290719032</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.000135440985654</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.00174017995595932</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.000135357959823</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002303289249539375</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.000135150395246</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.002342367544770241</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.000135164232885</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.002128733322024345</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.000135302609269</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001973455771803856</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.000135018937681</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002250958234071732</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.0001348459672</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.001375520601868629</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.000134742184912</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001680923625826836</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.000134887480115</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002221405506134033</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.000135129638789</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001777702942490578</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.000134956668308</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002216534689068794</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.000134659159081</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.001447796821594238</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.000134645321442</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00193084217607975</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.000134278624023</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.001757010817527771</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.000134278624023</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0004180856049060822</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.00013421635465</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.001545118167996407</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.000134112572362</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.001883501186966896</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.000133939601881</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001400535926222801</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.000133988033615</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.001665335148572922</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.000133628255015</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.002013685181736946</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.0001335867421</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.001525001600384712</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.000133642092654</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.001982465386390686</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.000133697443208</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.001934407278895378</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.000133738956123</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002069359645247459</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.000133469122173</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002062970772385597</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.000133524472727</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002062825486063957</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.000133669767931</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002095866948366165</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.000133635173834</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002218997105956078</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.000133621336196</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00159393809735775</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.000133711280846</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.00041944719851017</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.000134029546531</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001091504469513893</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7902284144202447</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.000133849657231</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.001645056530833244</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1945034831113877</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.000133891170146</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.001904955133795738</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1945034831113877</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.000133704362027</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001991456374526024</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3945034831113877</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.000133773550219</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001756932586431503</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.000133572904461</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002047019079327583</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.000133614417377</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0019088014960289</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3945034831113877</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.000133642092654</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_4_000006.xlsx
+++ b/out/Attention-Mamba1_repeat_4_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.001149719581007957</v>
+        <v>-0.001149712130427361</v>
       </c>
       <c r="JB2" t="n">
         <v>0.2599999999999997</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.001093912869691849</v>
+        <v>-0.001093903556466103</v>
       </c>
       <c r="JB3" t="n">
         <v>0.04999999999999971</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.001104498282074928</v>
+        <v>-0.001104490831494331</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001155907288193703</v>
+        <v>-0.001155892387032509</v>
       </c>
       <c r="JB5" t="n">
         <v>0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001549901440739632</v>
+        <v>-0.001549927517771721</v>
       </c>
       <c r="JB6" t="n">
         <v>0.16</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001257250085473061</v>
+        <v>-0.00125722773373127</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.5799999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.001570826396346092</v>
+        <v>-0.001570833846926689</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.5799999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.001206373795866966</v>
+        <v>-0.001206381246447563</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.001257086172699928</v>
+        <v>-0.001257088035345078</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.001694208011031151</v>
+        <v>-0.00169418565928936</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.7199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.001719655469059944</v>
+        <v>-0.001719648018479347</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.8599999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.001840399578213692</v>
+        <v>-0.001840388402342796</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.001553555950522423</v>
+        <v>-0.001553535461425781</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.001945154741406441</v>
+        <v>-0.001945158466696739</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.002032382413744926</v>
+        <v>-0.00203237496316433</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.002063222229480743</v>
+        <v>-0.002063235267996788</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.001819757744669914</v>
+        <v>-0.001819739118218422</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.001610806211829185</v>
+        <v>-0.00161079503595829</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.001261170953512192</v>
+        <v>-0.001261178404092789</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.1199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.001651650294661522</v>
+        <v>-0.001651657745242119</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.1199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.00179041363298893</v>
+        <v>-0.001790430396795273</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.00193432904779911</v>
+        <v>-0.001934336498379707</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.2599999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.001939682289958</v>
+        <v>-0.001939674839377403</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.2599999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.00142686627805233</v>
+        <v>-0.001426847651600838</v>
       </c>
       <c r="JB25" t="n">
         <v>0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.001941932365298271</v>
+        <v>-0.00194193422794342</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.000985490158200264</v>
+        <v>-0.0009854882955551147</v>
       </c>
       <c r="JB27" t="n">
         <v>0.5799999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.000218292698264122</v>
+        <v>0.0002183131873607635</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0008589606732130051</v>
+        <v>-0.000858968123793602</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.001233404502272606</v>
+        <v>-0.001233430579304695</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.001110436394810677</v>
+        <v>-0.001110440120100975</v>
       </c>
       <c r="JB31" t="n">
         <v>0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.00164218433201313</v>
+        <v>-0.001642169430851936</v>
       </c>
       <c r="JB32" t="n">
         <v>0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.001874817535281181</v>
+        <v>-0.001874810084700584</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.001637896522879601</v>
+        <v>-0.001637892797589302</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0006378982216119766</v>
+        <v>-0.000637909397482872</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.001331793144345284</v>
+        <v>-0.001331789419054985</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.001297602429986</v>
+        <v>-0.001297615468502045</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.001015147194266319</v>
+        <v>-0.001015136018395424</v>
       </c>
       <c r="JB38" t="n">
         <v>0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.001502742990851402</v>
+        <v>-0.001502728089690208</v>
       </c>
       <c r="JB39" t="n">
         <v>0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.001310920342803001</v>
+        <v>-0.001310905441641808</v>
       </c>
       <c r="JB40" t="n">
         <v>0.7199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0009707864373922348</v>
+        <v>-0.0009707901626825333</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0003504734486341476</v>
+        <v>-0.0003504622727632523</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.0001511033624410629</v>
+        <v>0.0001510791480541229</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.001502273604273796</v>
+        <v>0.001502266153693199</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.001021979376673698</v>
+        <v>0.001021977514028549</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0006977580487728119</v>
+        <v>-0.0006977561861276627</v>
       </c>
       <c r="JB46" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-6.519816815853119e-05</v>
+        <v>-6.520561873912811e-05</v>
       </c>
       <c r="JB47" t="n">
         <v>0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.0001495927572250366</v>
+        <v>-0.0001495946198701859</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.02000000000000007</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0007520373910665512</v>
+        <v>-0.0007520392537117004</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.0004364103078842163</v>
+        <v>0.000436415895819664</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.02000000000000007</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>7.568858563899994e-05</v>
+        <v>7.568486034870148e-05</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.0001615341752767563</v>
+        <v>0.0001615099608898163</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0006300788372755051</v>
+        <v>-0.0006300639361143112</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.001656441017985344</v>
+        <v>0.001656444743275642</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0008706841617822647</v>
+        <v>-0.0008706972002983093</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.00293884240090847</v>
+        <v>0.002938849851489067</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.002332659438252449</v>
+        <v>-0.002332661300897598</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.00552862323820591</v>
+        <v>-0.005528612062335014</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.1600000000000001</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.005274025723338127</v>
+        <v>0.005274014547467232</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.4399999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.005262864753603935</v>
+        <v>0.005262875929474831</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0009346604347229004</v>
+        <v>-0.0009346753358840942</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1600000000000001</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.002454893663525581</v>
+        <v>-0.002454882487654686</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.0004567783325910568</v>
+        <v>0.0004567559808492661</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.001624139025807381</v>
+        <v>-0.001624142751097679</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.7199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.00135795958340168</v>
+        <v>-0.001357974484562874</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.001973794773221016</v>
+        <v>-0.001973824575543404</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.8599999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.001015087589621544</v>
+        <v>-0.001015085726976395</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.8599999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.0002600569278001785</v>
+        <v>0.000260060653090477</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.8599999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0009745452553033829</v>
+        <v>-0.0009745582938194275</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0005184095352888107</v>
+        <v>-0.0005183909088373184</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.002309849485754967</v>
+        <v>-0.002309845760464668</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.001269010826945305</v>
+        <v>-0.001269025728106499</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0.9559192023383496</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.001947948709130287</v>
+        <v>-0.001947926357388496</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC73" t="n">
         <v>0.9559183444047648</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0003470946103334427</v>
+        <v>-0.0003470871597528458</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
         <v>0.9559185727257994</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0002161022275686264</v>
+        <v>-0.0002160947769880295</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
         <v>0.9559177770615876</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.001512933522462845</v>
+        <v>-0.0015129204839468</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC76" t="n">
         <v>0.9559178393309608</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001611316576600075</v>
+        <v>-0.001611322164535522</v>
       </c>
       <c r="JB77" t="n">
         <v>0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.0003103259950876236</v>
+        <v>-0.0003103390336036682</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001415975391864777</v>
+        <v>-0.001415988430380821</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0.9559176732792992</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.001457519829273224</v>
+        <v>-0.001457525417208672</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0.9559177493863108</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002230484038591385</v>
+        <v>-0.002230502665042877</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0.9559179154379724</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.00086217001080513</v>
+        <v>-0.0008621718734502792</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0.9559182752165725</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.0001916978508234024</v>
+        <v>-0.0001916959881782532</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0.9559182959730301</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.0002622436732053757</v>
+        <v>0.0002622473984956741</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0.9559183997553187</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001870037987828255</v>
+        <v>-0.001870039850473404</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002738794311881065</v>
+        <v>-0.002738809213042259</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003211705014109612</v>
+        <v>-0.003211701288819313</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.001273661851882935</v>
+        <v>-0.001273667439818382</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.001403609290719032</v>
+        <v>-0.001403648406267166</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.00174017995595932</v>
+        <v>-0.001740191131830215</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002303289249539375</v>
+        <v>-0.00230327807366848</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.002342367544770241</v>
+        <v>-0.002342399209737778</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.002128733322024345</v>
+        <v>-0.002128718420863152</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.001973455771803856</v>
+        <v>-0.001973452046513557</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.8599999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.002250958234071732</v>
+        <v>-0.002250948920845985</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.2599999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.001375520601868629</v>
+        <v>-0.001375501975417137</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.2599999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.001680923625826836</v>
+        <v>-0.001680932939052582</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.2599999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.002221405506134033</v>
+        <v>-0.002221418544650078</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.2599999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.001777702942490578</v>
+        <v>-0.001777684316039085</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.2599999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.002216534689068794</v>
+        <v>-0.002216549590229988</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.2599999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.001447796821594238</v>
+        <v>-0.001447791233658791</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.2599999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.00193084217607975</v>
+        <v>-0.001930871978402138</v>
       </c>
       <c r="JB102" t="n">
         <v>0.02000000000000007</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.001757010817527771</v>
+        <v>-0.001757001504302025</v>
       </c>
       <c r="JB103" t="n">
         <v>0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.0004180856049060822</v>
+        <v>-0.0004181079566478729</v>
       </c>
       <c r="JB104" t="n">
         <v>0.1600000000000001</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.001545118167996407</v>
+        <v>-0.001545114442706108</v>
       </c>
       <c r="JB105" t="n">
         <v>0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.001883501186966896</v>
+        <v>-0.001883497461676598</v>
       </c>
       <c r="JB106" t="n">
         <v>0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001400535926222801</v>
+        <v>-0.001400554552674294</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.001665335148572922</v>
+        <v>-0.001665337011218071</v>
       </c>
       <c r="JB108" t="n">
         <v>0.3</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.002013685181736946</v>
+        <v>-0.002013666555285454</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.001525001600384712</v>
+        <v>-0.001524994149804115</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.001982465386390686</v>
+        <v>-0.001982463523745537</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.001934407278895378</v>
+        <v>-0.001934373751282692</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002069359645247459</v>
+        <v>-0.002069389447569847</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.002062970772385597</v>
+        <v>-0.002062959596514702</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002062825486063957</v>
+        <v>-0.002062847837805748</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002095866948366165</v>
+        <v>-0.002095906063914299</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.00159393809735775</v>
+        <v>-0.001593947410583496</v>
       </c>
       <c r="JB118" t="n">
         <v>0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.00041944719851017</v>
+        <v>0.0004194695502519608</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.001091504469513893</v>
+        <v>-0.001091483980417252</v>
       </c>
       <c r="JB120" t="n">
         <v>0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.001645056530833244</v>
+        <v>-0.001645060256123543</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.001904955133795738</v>
+        <v>-0.001904949545860291</v>
       </c>
       <c r="JB122" t="n">
         <v>0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.001991456374526024</v>
+        <v>-0.001991452649235725</v>
       </c>
       <c r="JB123" t="n">
         <v>0.02000000000000007</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.001756932586431503</v>
+        <v>-0.001756949350237846</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.8599999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002047019079327583</v>
+        <v>-0.002047011628746986</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.8599999999999997</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.0019088014960289</v>
+        <v>-0.001908797770738602</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.8599999999999997</v>
